--- a/output/pdf_financials_xlsx/HPL.xlsx
+++ b/output/pdf_financials_xlsx/HPL.xlsx
@@ -1505,19 +1505,19 @@
         <v>0.5627490000000001</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.084664</v>
+        <v>-0.084664</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.328085</v>
+        <v>-0.328085</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>1.15734</v>
+        <v>-1.15734</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>1.187808</v>
+        <v>-1.187808</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>3.25417</v>
+        <v>-3.25417</v>
       </c>
     </row>
     <row r="17">
@@ -1837,19 +1837,19 @@
         <v>0.5627490000000001</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.084664</v>
+        <v>-0.084664</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.328085</v>
+        <v>-0.328085</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>1.15734</v>
+        <v>-1.15734</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>1.187808</v>
+        <v>-1.187808</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>3.25417</v>
+        <v>-3.25417</v>
       </c>
     </row>
     <row r="21">
@@ -2059,19 +2059,19 @@
         <v>0.5627490000000001</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.084664</v>
+        <v>-0.084664</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>0.328085</v>
+        <v>-0.328085</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>1.15734</v>
+        <v>-1.15734</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>1.187808</v>
+        <v>-1.187808</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>3.25417</v>
+        <v>-3.25417</v>
       </c>
     </row>
     <row r="24">
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-16.40425</v>
+        <v>16.40425</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-23.1468</v>
+        <v>23.1468</v>
       </c>
       <c r="Q26" s="1" t="inlineStr">
         <is>
@@ -2375,19 +2375,19 @@
         <v>0.5627490000000001</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.084664</v>
+        <v>-0.084664</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.328085</v>
+        <v>-0.328085</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>1.15734</v>
+        <v>-1.15734</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>1.187808</v>
+        <v>-1.187808</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>3.25417</v>
+        <v>-3.25417</v>
       </c>
     </row>
     <row r="28">
@@ -2523,19 +2523,19 @@
         <v>0.5627490000000001</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.084664</v>
+        <v>-0.084664</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.328085</v>
+        <v>-0.328085</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1.15734</v>
+        <v>-1.15734</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>1.187808</v>
+        <v>-1.187808</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>3.25417</v>
+        <v>-3.25417</v>
       </c>
     </row>
     <row r="30">
@@ -2689,19 +2689,19 @@
         <v>0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -6484,28 +6484,28 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.09897300000000001</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.126302</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.137921</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.428854</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.451619</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.574311</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.624754</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.854196</v>
       </c>
       <c r="L92" s="3" t="n">
         <v>0</v>
@@ -15185,7 +15185,11 @@
           <t>Reserve (note 13)</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -16088,7 +16092,11 @@
           <t>Reserves (note 13)</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -16593,7 +16601,11 @@
           <t>Reserves (note 11)</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -17395,7 +17407,11 @@
           <t>Reserves (note 10)</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -18813,7 +18829,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -34007,10 +34027,10 @@
         </is>
       </c>
       <c r="Q242" s="5" t="n">
-        <v>0.084664</v>
+        <v>-0.084664</v>
       </c>
       <c r="R242" s="5" t="n">
-        <v>0.328085</v>
+        <v>-0.328085</v>
       </c>
       <c r="S242" t="inlineStr">
         <is>
@@ -34018,10 +34038,10 @@
         </is>
       </c>
       <c r="T242" s="5" t="n">
-        <v>1.187808</v>
+        <v>-1.187808</v>
       </c>
       <c r="U242" s="5" t="n">
-        <v>3.25417</v>
+        <v>-3.25417</v>
       </c>
     </row>
     <row r="243">
@@ -35006,13 +35026,13 @@
         </is>
       </c>
       <c r="R252" s="5" t="n">
-        <v>0.328085</v>
+        <v>-0.328085</v>
       </c>
       <c r="S252" s="5" t="n">
-        <v>1.15734</v>
+        <v>-1.15734</v>
       </c>
       <c r="T252" s="5" t="n">
-        <v>1.187808</v>
+        <v>-1.187808</v>
       </c>
       <c r="U252" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/HPL.xlsx
+++ b/output/pdf_financials_xlsx/HPL.xlsx
@@ -1055,22 +1055,22 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.467313</v>
+        <v>3.593783</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.102165</v>
+        <v>0.5627490000000001</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.05962</v>
+        <v>0.084664</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.04213</v>
+        <v>0.328085</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.629265</v>
+        <v>1.155097</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.662367</v>
+        <v>1.187808</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>1.815562</v>
@@ -1129,22 +1129,22 @@
         </is>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.467313</v>
+        <v>-3.593783</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.102165</v>
+        <v>-0.5627490000000001</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.05962</v>
+        <v>-0.084664</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.04213</v>
+        <v>-0.328085</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.629265</v>
+        <v>-1.155097</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.662367</v>
+        <v>-1.187808</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>-1.815562</v>
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.005951</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-3.587832</v>
+        <v>-3.593783</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>0.5627490000000001</v>
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-3.587832</v>
+        <v>-3.593783</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>0.5627490000000001</v>
@@ -2815,16 +2815,16 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.000606</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.819072</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.604537</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.503467</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0</v>
@@ -2842,25 +2842,25 @@
         <v>0.168235</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.220144</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.04722</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.050804</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.020174</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.158841</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.076408</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.111385</v>
       </c>
     </row>
     <row r="35">
@@ -2935,16 +2935,16 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.000606</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.819072</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.604537</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.503467</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0</v>
@@ -2962,25 +2962,25 @@
         <v>0.168235</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.220144</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.04722</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.050804</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.020174</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.158841</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.076408</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.111385</v>
       </c>
     </row>
     <row r="37">
@@ -3655,16 +3655,16 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.000606</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.819072</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.604537</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.514534</v>
+        <v>0.011067</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>1.01629</v>
@@ -3682,10 +3682,10 @@
         <v>0.016293</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.242836</v>
+        <v>0.022692</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.053378</v>
+        <v>0.006158</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0</v>
@@ -9775,7 +9775,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -17613,7 +17613,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -33858,7 +33858,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -34763,7 +34763,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -34820,7 +34820,7 @@
         <v>3.593783</v>
       </c>
       <c r="P250" s="5" t="n">
-        <v>-0.5627490000000001</v>
+        <v>0.5627490000000001</v>
       </c>
       <c r="Q250" s="5" t="n">
         <v>0.084664</v>
@@ -35866,7 +35866,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -37488,7 +37488,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
